--- a/output/pdf_financials_xlsx/PCQ.xlsx
+++ b/output/pdf_financials_xlsx/PCQ.xlsx
@@ -4796,43 +4796,43 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.8844070000000001</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.815248</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.750119</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.706027</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.369024</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.366885</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.878183</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.119574</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.313747</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.119426</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.749254</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.741001</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.99664</v>
       </c>
     </row>
     <row r="93">
@@ -8670,7 +8670,11 @@
           <t>Reserves (notes 11 and 12)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -9896,7 +9900,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -10354,7 +10362,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -10761,7 +10773,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -11154,7 +11170,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -12185,7 +12205,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" s="5" t="n">
         <v>0.8844070000000001</v>
       </c>

--- a/output/pdf_financials_xlsx/PCQ.xlsx
+++ b/output/pdf_financials_xlsx/PCQ.xlsx
@@ -909,19 +909,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000104</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>8.1e-05</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000123</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>7.1e-05</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000138</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1729,19 +1729,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.163929</v>
+        <v>-1.164033</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.22654</v>
+        <v>-1.226621</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.636443</v>
+        <v>-0.636566</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.886758</v>
+        <v>-0.886829</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.506844</v>
+        <v>-0.506982</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.995366</v>
@@ -1821,19 +1821,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.163929</v>
+        <v>-1.164033</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.22654</v>
+        <v>-1.226621</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.636443</v>
+        <v>-0.636566</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.886758</v>
+        <v>-0.886829</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.506844</v>
+        <v>-0.506982</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.995366</v>
@@ -13368,7 +13368,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -15043,7 +15043,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">

--- a/output/pdf_financials_xlsx/PCQ.xlsx
+++ b/output/pdf_financials_xlsx/PCQ.xlsx
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.033192</v>
+        <v>-0.033192</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
@@ -3628,19 +3628,19 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.147677</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.09714100000000001</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.057988</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.045582</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.080956</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0</v>
@@ -17232,7 +17232,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E121" s="5" t="n">
         <v>0.033192</v>
       </c>
